--- a/documentation/KPI_dictionary.xlsx
+++ b/documentation/KPI_dictionary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E662436B-0136-924C-9E12-4179770A4487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="32960" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI Dictionary" sheetId="1" r:id="rId1"/>
